--- a/artfynd/A 34496-2026 artfynd.xlsx
+++ b/artfynd/A 34496-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136313169</v>
       </c>
       <c r="B2" t="n">
-        <v>97954</v>
+        <v>97957</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136312969</v>
       </c>
       <c r="B3" t="n">
-        <v>96567</v>
+        <v>96570</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34496-2026 artfynd.xlsx
+++ b/artfynd/A 34496-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136313169</v>
       </c>
       <c r="B2" t="n">
-        <v>97957</v>
+        <v>97958</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136312969</v>
       </c>
       <c r="B3" t="n">
-        <v>96570</v>
+        <v>96571</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34496-2026 artfynd.xlsx
+++ b/artfynd/A 34496-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136313169</v>
       </c>
       <c r="B2" t="n">
-        <v>97958</v>
+        <v>97963</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136312969</v>
       </c>
       <c r="B3" t="n">
-        <v>96571</v>
+        <v>96576</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>136312967</v>
       </c>
       <c r="B6" t="n">
-        <v>56570</v>
+        <v>56572</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34496-2026 artfynd.xlsx
+++ b/artfynd/A 34496-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136313169</v>
       </c>
       <c r="B2" t="n">
-        <v>97963</v>
+        <v>97965</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136312969</v>
       </c>
       <c r="B3" t="n">
-        <v>96576</v>
+        <v>96578</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34496-2026 artfynd.xlsx
+++ b/artfynd/A 34496-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136313169</v>
       </c>
       <c r="B2" t="n">
-        <v>97965</v>
+        <v>97971</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136312969</v>
       </c>
       <c r="B3" t="n">
-        <v>96578</v>
+        <v>96584</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34496-2026 artfynd.xlsx
+++ b/artfynd/A 34496-2026 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>136313461</v>
       </c>
       <c r="B4" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136313462</v>
       </c>
       <c r="B5" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
